--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N59_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N59_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.24670822717614</v>
+        <v>1.990090086916123</v>
       </c>
       <c r="D2" t="n">
-        <v>11.98654642284061</v>
+        <v>1.9478137937116</v>
       </c>
       <c r="E2" t="n">
-        <v>16.96716709343228</v>
+        <v>2.757164652682746</v>
       </c>
       <c r="F2" t="n">
-        <v>16.94976918566875</v>
+        <v>2.754337492671173</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.86984603164473</v>
+        <v>5.828849980142269</v>
       </c>
       <c r="D3" t="n">
-        <v>39.62838889139643</v>
+        <v>6.439613194851919</v>
       </c>
       <c r="E3" t="n">
-        <v>16.96716709343228</v>
+        <v>2.757164652682746</v>
       </c>
       <c r="F3" t="n">
-        <v>16.94976918566875</v>
+        <v>2.754337492671173</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.90068121550246</v>
+        <v>7.94636069751915</v>
       </c>
       <c r="D4" t="n">
-        <v>49.01257045901701</v>
+        <v>7.964542699590264</v>
       </c>
       <c r="E4" t="n">
-        <v>16.96716709343228</v>
+        <v>2.757164652682746</v>
       </c>
       <c r="F4" t="n">
-        <v>16.94976918566875</v>
+        <v>2.754337492671173</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.40134633125228</v>
+        <v>8.840218778828495</v>
       </c>
       <c r="D5" t="n">
-        <v>54.70025109425369</v>
+        <v>8.888790802816224</v>
       </c>
       <c r="E5" t="n">
-        <v>16.96716709343228</v>
+        <v>2.757164652682746</v>
       </c>
       <c r="F5" t="n">
-        <v>16.94976918566875</v>
+        <v>2.754337492671173</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>59.76097165401944</v>
+        <v>9.711157893778159</v>
       </c>
       <c r="D6" t="n">
-        <v>60.03675460633966</v>
+        <v>9.755972623530194</v>
       </c>
       <c r="E6" t="n">
-        <v>16.96716709343228</v>
+        <v>2.757164652682746</v>
       </c>
       <c r="F6" t="n">
-        <v>16.94976918566875</v>
+        <v>2.754337492671173</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
